--- a/artifacts/demo_rehearsal/DEMONSTRATION_WALKTHROUGH_EXAMPLES_system_groups.xlsx
+++ b/artifacts/demo_rehearsal/DEMONSTRATION_WALKTHROUGH_EXAMPLES_system_groups.xlsx
@@ -7,12 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Candidate Groups" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Group Data" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Review Groups" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Group Index" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Detailed Data" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Technical Reference" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Candidate Groups'!$A$1:$I$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Group Index'!$A$1:$H$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Technical Reference'!$A$1:$I$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,18 +34,27 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="16"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="20"/>
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00243746"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <color rgb="00243746"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -56,11 +68,46 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF3F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3F5F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005B7894"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4DFEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -82,31 +129,175 @@
         <color rgb="00B7C9D6"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B7C9D6"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B7C9D6"/>
+      </right>
+      <top style="medium">
+        <color rgb="006C8FA5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B7C9D6"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B7C9D6"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B7C9D6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B7C9D6"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="006C8FA5"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B7C9D6"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B7C9D6"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B7C9D6"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B7C9D6"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B7C9D6"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00B7C9D6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -186,32 +377,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SystemGroupData" displayName="SystemGroupData" ref="A1:W10" headerRowCount="1">
-  <autoFilter ref="A1:W10"/>
-  <tableColumns count="23">
-    <tableColumn id="1" name="Candidate Group ID"/>
-    <tableColumn id="2" name="Canonical Group ID"/>
-    <tableColumn id="3" name="Review State"/>
-    <tableColumn id="4" name="System Evidence Tier"/>
-    <tableColumn id="5" name="Member Count"/>
-    <tableColumn id="6" name="Sites"/>
-    <tableColumn id="7" name="Primary Reason"/>
-    <tableColumn id="8" name="Human Decision"/>
-    <tableColumn id="9" name="Human Comment"/>
-    <tableColumn id="10" name="Part No"/>
-    <tableColumn id="11" name="Description"/>
-    <tableColumn id="12" name="Site"/>
-    <tableColumn id="13" name="Inventory UOM"/>
-    <tableColumn id="14" name="Part Type"/>
-    <tableColumn id="15" name="Commodity Group 01"/>
-    <tableColumn id="16" name="Commodity Group 02"/>
-    <tableColumn id="17" name="Safety Code"/>
-    <tableColumn id="18" name="Accounting Group"/>
-    <tableColumn id="19" name="Product Code"/>
-    <tableColumn id="20" name="Product Family"/>
-    <tableColumn id="21" name="Product Category"/>
-    <tableColumn id="22" name="HSN/SAC Code"/>
-    <tableColumn id="23" name="Source Row / Stable Record Reference"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SystemGroupData" displayName="SystemGroupData" ref="A1:T10" headerRowCount="1">
+  <autoFilter ref="A1:T10"/>
+  <tableColumns count="20">
+    <tableColumn id="1" name="Group"/>
+    <tableColumn id="2" name="Review Status"/>
+    <tableColumn id="3" name="Evidence"/>
+    <tableColumn id="4" name="Members"/>
+    <tableColumn id="5" name="Group Sites"/>
+    <tableColumn id="6" name="Human Decision"/>
+    <tableColumn id="7" name="Human Comment"/>
+    <tableColumn id="8" name="Part Number"/>
+    <tableColumn id="9" name="Description"/>
+    <tableColumn id="10" name="Site"/>
+    <tableColumn id="11" name="Inventory UOM"/>
+    <tableColumn id="12" name="Part Type"/>
+    <tableColumn id="13" name="Commodity Group 01"/>
+    <tableColumn id="14" name="Commodity Group 02"/>
+    <tableColumn id="15" name="Safety Code"/>
+    <tableColumn id="16" name="Accounting Group"/>
+    <tableColumn id="17" name="Product Code"/>
+    <tableColumn id="18" name="Product Family"/>
+    <tableColumn id="19" name="Product Category"/>
+    <tableColumn id="20" name="HSN/SAC Code"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -506,238 +694,388 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Inventory Identity Review Candidate Report</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Purpose</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Inventory identity review candidate report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Important</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>System-generated groups are suggestions requiring human review. They are not automatic merge instructions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+    </row>
+    <row r="4" ht="26" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Human authority</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Confirmed, rejected, or deferred human decisions override the system suggestion.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Workflow</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>System suggests -&gt; Human reviews -&gt; Human decision becomes authoritative</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Report authority</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Advisory system suggestions with explicit human-review state</t>
-        </is>
-      </c>
+          <t>System-generated groups are suggestions requiring human review. They are not automatic merge instructions. Human decisions are authoritative and override system suggestions.</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Scan identifier</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Input Records</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Candidate Groups</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Stronger Evidence</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Needs Additional Review</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="6" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Scan name</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" s="7" t="n"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="7" t="n"/>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Human Confirmed</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Human Rejected</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Deferred / Unreviewed</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Conflicts / Deferred Work</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n"/>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="9" t="n"/>
+      <c r="G12" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" s="9" t="n"/>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="9" t="n"/>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="9" t="n"/>
+      <c r="H13" s="9" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>How to use this workbook</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>1. Start with Review Groups.
+2. Review the records inside each candidate group.
+3. System evidence is advisory.
+4. Human decisions are authoritative.</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="12" t="n"/>
+      <c r="H16" s="12" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="n"/>
+      <c r="B17" s="12" t="n"/>
+      <c r="C17" s="12" t="n"/>
+      <c r="D17" s="12" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="12" t="n"/>
+      <c r="G17" s="12" t="n"/>
+      <c r="H17" s="12" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="n"/>
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="12" t="n"/>
+      <c r="D18" s="12" t="n"/>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="12" t="n"/>
+      <c r="G18" s="12" t="n"/>
+      <c r="H18" s="12" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="n"/>
+      <c r="B19" s="12" t="n"/>
+      <c r="C19" s="12" t="n"/>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="12" t="n"/>
+      <c r="G19" s="12" t="n"/>
+      <c r="H19" s="12" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>Report details</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="14" t="n"/>
+      <c r="D21" s="14" t="n"/>
+      <c r="E21" s="14" t="n"/>
+      <c r="F21" s="14" t="n"/>
+      <c r="G21" s="14" t="n"/>
+      <c r="H21" s="14" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>Scan ID</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="12" t="n"/>
+      <c r="F22" s="12" t="n"/>
+      <c r="G22" s="12" t="n"/>
+      <c r="H22" s="12" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>Scan Name</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="16" t="inlineStr">
         <is>
           <t>DEMONSTRATION / WALKTHROUGH EXAMPLES - Final Rehearsal</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Scan status</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="D23" s="12" t="n"/>
+      <c r="E23" s="12" t="n"/>
+      <c r="F23" s="12" t="n"/>
+      <c r="G23" s="12" t="n"/>
+      <c r="H23" s="12" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>Scan Status</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="16" t="inlineStr">
         <is>
           <t>COMPLETED</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Input record count</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>System-Suggested Candidate Groups</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Human Confirmed Groups</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="12" t="n"/>
+      <c r="F24" s="12" t="n"/>
+      <c r="G24" s="12" t="n"/>
+      <c r="H24" s="12" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>Projection Contract</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>G2_V2</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="12" t="n"/>
+      <c r="G25" s="12" t="n"/>
+      <c r="H25" s="12" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>Source Projection Run</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="16" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Human Rejected Candidates</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Review Deferred / Unreviewed</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Stronger Evidence candidates</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Review Evidence candidates</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Conflict count</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Deferred count</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Unassigned count</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="12" t="n"/>
+      <c r="F26" s="12" t="n"/>
+      <c r="G26" s="12" t="n"/>
+      <c r="H26" s="12" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>Unassigned Records</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="16" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Projection contract</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>G2_V2</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Source projection run</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="12" t="n"/>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12" t="n"/>
+      <c r="H27" s="12" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="33">
+    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="A12:B13"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="A4:H5"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C27:H27"/>
+    <mergeCell ref="C23:H23"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="E12:F13"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="G12:H13"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="G8:H9"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C24:H24"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="A16:H19"/>
+    <mergeCell ref="C26:H26"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -748,259 +1086,683 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="54" customWidth="1" min="7" max="7"/>
-    <col width="38" customWidth="1" min="8" max="8"/>
-    <col width="42" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="48" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="20" customWidth="1" min="21" max="21"/>
-    <col width="18" customWidth="1" min="22" max="22"/>
-    <col width="48" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="34" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Candidate Group ID</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="B1" s="5" t="inlineStr">
         <is>
-          <t>Canonical Group ID</t>
+          <t>Review Status</t>
         </is>
       </c>
       <c r="C1" s="5" t="inlineStr">
         <is>
-          <t>Review State</t>
+          <t>Evidence</t>
         </is>
       </c>
       <c r="D1" s="5" t="inlineStr">
         <is>
-          <t>System Evidence Tier</t>
+          <t>Group Sites</t>
         </is>
       </c>
       <c r="E1" s="5" t="inlineStr">
         <is>
-          <t>Member Count</t>
+          <t>Why Suggested</t>
         </is>
       </c>
       <c r="F1" s="5" t="inlineStr">
         <is>
-          <t>Sites</t>
+          <t>Human Decision</t>
         </is>
       </c>
       <c r="G1" s="5" t="inlineStr">
         <is>
-          <t>Primary Reason</t>
+          <t>Human Comment</t>
         </is>
       </c>
       <c r="H1" s="5" t="inlineStr">
         <is>
-          <t>Human Decision</t>
+          <t>Member #</t>
         </is>
       </c>
       <c r="I1" s="5" t="inlineStr">
         <is>
-          <t>Human Comment</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+          <t>Part Number</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>Site</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>UOM</t>
+        </is>
+      </c>
+      <c r="M1" s="5" t="inlineStr">
+        <is>
+          <t>Part Type</t>
+        </is>
+      </c>
+      <c r="N1" s="5" t="inlineStr">
+        <is>
+          <t>Commodity Group 01</t>
+        </is>
+      </c>
+      <c r="O1" s="5" t="inlineStr">
+        <is>
+          <t>Commodity Group 02</t>
+        </is>
+      </c>
+      <c r="P1" s="5" t="inlineStr">
+        <is>
+          <t>Safety Code</t>
+        </is>
+      </c>
+      <c r="Q1" s="5" t="inlineStr">
+        <is>
+          <t>Accounting Group</t>
+        </is>
+      </c>
+      <c r="R1" s="5" t="inlineStr">
+        <is>
+          <t>Product Code</t>
+        </is>
+      </c>
+      <c r="S1" s="5" t="inlineStr">
+        <is>
+          <t>Product Family</t>
+        </is>
+      </c>
+      <c r="T1" s="5" t="inlineStr">
+        <is>
+          <t>Product Category</t>
+        </is>
+      </c>
+      <c r="U1" s="5" t="inlineStr">
+        <is>
+          <t>HSN/SAC Code</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>CG-000001</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>igk1.eyJnIjoiZzJ2Mi1ncm91cC0xMjI1ZGUzNzUzMWNlNTg3ZThiNzBhNjIzNDE0NjYxMzI2OWJmOTM1ZTIyYTQzNTQxMTI3YzE0ZWUzZWEwNGU2IiwicCI6IkcyX1YyIiwicyI6MX0</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="B2" s="18" t="inlineStr">
         <is>
           <t>Review Deferred</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="C2" s="17" t="inlineStr">
         <is>
           <t>Review Evidence</t>
         </is>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="D2" s="17" t="inlineStr">
+        <is>
+          <t>SITE-TEMP</t>
+        </is>
+      </c>
+      <c r="E2" s="17" t="inlineStr">
+        <is>
+          <t>Some identity signals match; manual assessment is needed.</t>
+        </is>
+      </c>
+      <c r="F2" s="17" t="inlineStr">
+        <is>
+          <t>Deferred for later review</t>
+        </is>
+      </c>
+      <c r="G2" s="17" t="inlineStr">
+        <is>
+          <t>Walkthrough defer on synthetic examples; additional review is required.</t>
+        </is>
+      </c>
+      <c r="H2" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="19" t="inlineStr">
+        <is>
+          <t>TS-PT100-A</t>
+        </is>
+      </c>
+      <c r="J2" s="20" t="inlineStr">
+        <is>
+          <t>Temp sns PT100 0-200 C</t>
+        </is>
+      </c>
+      <c r="K2" s="19" t="inlineStr">
+        <is>
+          <t>SITE-TEMP</t>
+        </is>
+      </c>
+      <c r="L2" s="19" t="inlineStr">
+        <is>
+          <t>PCS</t>
+        </is>
+      </c>
+      <c r="M2" s="19" t="inlineStr"/>
+      <c r="N2" s="19" t="inlineStr"/>
+      <c r="O2" s="19" t="inlineStr"/>
+      <c r="P2" s="19" t="inlineStr"/>
+      <c r="Q2" s="19" t="inlineStr"/>
+      <c r="R2" s="19" t="inlineStr"/>
+      <c r="S2" s="19" t="inlineStr"/>
+      <c r="T2" s="19" t="inlineStr"/>
+      <c r="U2" s="19" t="inlineStr">
+        <is>
+          <t>9025</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="21" t="n"/>
+      <c r="B3" s="21" t="n"/>
+      <c r="C3" s="21" t="n"/>
+      <c r="D3" s="21" t="n"/>
+      <c r="E3" s="21" t="n"/>
+      <c r="F3" s="21" t="n"/>
+      <c r="G3" s="21" t="n"/>
+      <c r="H3" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
+        <is>
+          <t>SENSOR-PT100-B</t>
+        </is>
+      </c>
+      <c r="J3" s="23" t="inlineStr">
+        <is>
+          <t>Temperature sensor PT100 range 0 to 200 C</t>
+        </is>
+      </c>
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t>SITE-TEMP</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>Deterministic review evidence caused the system to suggest this group; human review is required.</t>
-        </is>
-      </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>Deferred for later review</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>Walkthrough defer on synthetic examples; additional review is required.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="L3" s="22" t="inlineStr">
+        <is>
+          <t>PCS</t>
+        </is>
+      </c>
+      <c r="M3" s="22" t="inlineStr"/>
+      <c r="N3" s="22" t="inlineStr"/>
+      <c r="O3" s="22" t="inlineStr"/>
+      <c r="P3" s="22" t="inlineStr"/>
+      <c r="Q3" s="22" t="inlineStr"/>
+      <c r="R3" s="22" t="inlineStr"/>
+      <c r="S3" s="22" t="inlineStr"/>
+      <c r="T3" s="22" t="inlineStr"/>
+      <c r="U3" s="22" t="inlineStr">
+        <is>
+          <t>9025</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>CG-000002</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>igk1.eyJnIjoiZzJ2Mi1ncm91cC02NzkzMTdlNTY2MzVmYzRmNGI2NjQ4MGJmMTZjZTY2N2Y4MGJmNWUwOTk2YWJhOTI0YjhhYzBlZTg3NmMzZjExIiwicCI6IkcyX1YyIiwicyI6MX0</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Requires Human Review</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>Stronger Evidence</t>
         </is>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>SITE-SEAL</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>Multiple deterministic identity signals support review.</t>
+        </is>
+      </c>
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <t>Not yet reviewed</t>
+        </is>
+      </c>
+      <c r="G4" s="24" t="inlineStr"/>
+      <c r="H4" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="26" t="inlineStr">
+        <is>
+          <t>SEAL-32-A</t>
+        </is>
+      </c>
+      <c r="J4" s="27" t="inlineStr">
+        <is>
+          <t>Mechanical seal for pump shaft 32 mm</t>
+        </is>
+      </c>
+      <c r="K4" s="26" t="inlineStr">
+        <is>
+          <t>SITE-SEAL</t>
+        </is>
+      </c>
+      <c r="L4" s="26" t="inlineStr">
+        <is>
+          <t>PCS</t>
+        </is>
+      </c>
+      <c r="M4" s="26" t="inlineStr"/>
+      <c r="N4" s="26" t="inlineStr"/>
+      <c r="O4" s="26" t="inlineStr"/>
+      <c r="P4" s="26" t="inlineStr"/>
+      <c r="Q4" s="26" t="inlineStr"/>
+      <c r="R4" s="26" t="inlineStr"/>
+      <c r="S4" s="26" t="inlineStr"/>
+      <c r="T4" s="26" t="inlineStr"/>
+      <c r="U4" s="26" t="inlineStr">
+        <is>
+          <t>8484</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="21" t="n"/>
+      <c r="B5" s="21" t="n"/>
+      <c r="C5" s="21" t="n"/>
+      <c r="D5" s="21" t="n"/>
+      <c r="E5" s="21" t="n"/>
+      <c r="F5" s="21" t="n"/>
+      <c r="G5" s="21" t="n"/>
+      <c r="H5" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="I5" s="28" t="inlineStr">
+        <is>
+          <t>MECH-SEAL-32B</t>
+        </is>
+      </c>
+      <c r="J5" s="29" t="inlineStr">
+        <is>
+          <t>Pump mechanical seal 32mm shaft</t>
+        </is>
+      </c>
+      <c r="K5" s="28" t="inlineStr">
         <is>
           <t>SITE-SEAL</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>Stronger deterministic evidence caused the system to suggest this group for human review.</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>Not yet reviewed</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="L5" s="28" t="inlineStr">
+        <is>
+          <t>PCS</t>
+        </is>
+      </c>
+      <c r="M5" s="28" t="inlineStr"/>
+      <c r="N5" s="28" t="inlineStr"/>
+      <c r="O5" s="28" t="inlineStr"/>
+      <c r="P5" s="28" t="inlineStr"/>
+      <c r="Q5" s="28" t="inlineStr"/>
+      <c r="R5" s="28" t="inlineStr"/>
+      <c r="S5" s="28" t="inlineStr"/>
+      <c r="T5" s="28" t="inlineStr"/>
+      <c r="U5" s="28" t="inlineStr">
+        <is>
+          <t>8484</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>CG-000003</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>igk1.eyJnIjoiZzJ2Mi1ncm91cC1iZTJmMTEzZjNmOWUyMjc2YzQxMzQ5MjQyMGU3NWQxYWE2NjUxYTc2NDFhNDNlYTczZjU5OTAxNmEyYWQ5NzU1IiwicCI6IkcyX1YyIiwicyI6MX0</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Human Rejected Candidate</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>Review Evidence</t>
         </is>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>SITE-GEN-FILTER</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>Some identity signals match; manual assessment is needed.</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>Rejected and kept separate</t>
+        </is>
+      </c>
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>Walkthrough rejection on synthetic examples; records remain separate.</t>
+        </is>
+      </c>
+      <c r="H6" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="19" t="inlineStr">
+        <is>
+          <t>FILTER-220-B</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr">
+        <is>
+          <t>Generator oil filter element model 220</t>
+        </is>
+      </c>
+      <c r="K6" s="19" t="inlineStr">
+        <is>
+          <t>SITE-GEN-FILTER</t>
+        </is>
+      </c>
+      <c r="L6" s="19" t="inlineStr">
+        <is>
+          <t>PCS</t>
+        </is>
+      </c>
+      <c r="M6" s="19" t="inlineStr"/>
+      <c r="N6" s="19" t="inlineStr"/>
+      <c r="O6" s="19" t="inlineStr"/>
+      <c r="P6" s="19" t="inlineStr"/>
+      <c r="Q6" s="19" t="inlineStr"/>
+      <c r="R6" s="19" t="inlineStr"/>
+      <c r="S6" s="19" t="inlineStr"/>
+      <c r="T6" s="19" t="inlineStr"/>
+      <c r="U6" s="19" t="inlineStr">
+        <is>
+          <t>8421</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="21" t="n"/>
+      <c r="B7" s="21" t="n"/>
+      <c r="C7" s="21" t="n"/>
+      <c r="D7" s="21" t="n"/>
+      <c r="E7" s="21" t="n"/>
+      <c r="F7" s="21" t="n"/>
+      <c r="G7" s="21" t="n"/>
+      <c r="H7" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="I7" s="22" t="inlineStr">
+        <is>
+          <t>GOF-220-A</t>
+        </is>
+      </c>
+      <c r="J7" s="23" t="inlineStr">
+        <is>
+          <t>Gen oil fltr element model 220</t>
+        </is>
+      </c>
+      <c r="K7" s="22" t="inlineStr">
         <is>
           <t>SITE-GEN-FILTER</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>Deterministic review evidence caused the system to suggest this group; human review is required.</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>Rejected and kept separate</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>Walkthrough rejection on synthetic examples; records remain separate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="L7" s="22" t="inlineStr">
+        <is>
+          <t>PCS</t>
+        </is>
+      </c>
+      <c r="M7" s="22" t="inlineStr"/>
+      <c r="N7" s="22" t="inlineStr"/>
+      <c r="O7" s="22" t="inlineStr"/>
+      <c r="P7" s="22" t="inlineStr"/>
+      <c r="Q7" s="22" t="inlineStr"/>
+      <c r="R7" s="22" t="inlineStr"/>
+      <c r="S7" s="22" t="inlineStr"/>
+      <c r="T7" s="22" t="inlineStr"/>
+      <c r="U7" s="22" t="inlineStr">
+        <is>
+          <t>8421</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>CG-000004</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>igk1.eyJnIjoiZzJ2Mi1ncm91cC1lNTM4MzJiZjMwMzNmNTVhNzZkMDI2YTFkYjNmODI2ZDI5NzhhNDk4OTU1N2U5Y2Y5OWYzNDE4NmU0Nzc3ZTM3IiwicCI6IkcyX1YyIiwicyI6MX0</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>Human Confirmed Same-Identity Group</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>Review Evidence</t>
         </is>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>SITE-MOTOR</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>Some identity signals match; manual assessment is needed.</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>Confirmed all records as one identity</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t>Walkthrough confirmation on synthetic examples; not quality evidence.</t>
+        </is>
+      </c>
+      <c r="H8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="26" t="inlineStr">
+        <is>
+          <t>MTR10K-C</t>
+        </is>
+      </c>
+      <c r="J8" s="27" t="inlineStr">
+        <is>
+          <t>Three phase electric motor 10 kW 415 V flange mounted</t>
+        </is>
+      </c>
+      <c r="K8" s="26" t="inlineStr">
+        <is>
+          <t>SITE-MOTOR</t>
+        </is>
+      </c>
+      <c r="L8" s="26" t="inlineStr">
+        <is>
+          <t>PCS</t>
+        </is>
+      </c>
+      <c r="M8" s="26" t="inlineStr"/>
+      <c r="N8" s="26" t="inlineStr"/>
+      <c r="O8" s="26" t="inlineStr"/>
+      <c r="P8" s="26" t="inlineStr"/>
+      <c r="Q8" s="26" t="inlineStr"/>
+      <c r="R8" s="26" t="inlineStr"/>
+      <c r="S8" s="26" t="inlineStr"/>
+      <c r="T8" s="26" t="inlineStr"/>
+      <c r="U8" s="26" t="inlineStr">
+        <is>
+          <t>8501</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="32" t="n"/>
+      <c r="B9" s="32" t="n"/>
+      <c r="C9" s="32" t="n"/>
+      <c r="D9" s="32" t="n"/>
+      <c r="E9" s="32" t="n"/>
+      <c r="F9" s="32" t="n"/>
+      <c r="G9" s="32" t="n"/>
+      <c r="H9" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="33" t="inlineStr">
+        <is>
+          <t>MOTOR10K-B</t>
+        </is>
+      </c>
+      <c r="J9" s="34" t="inlineStr">
+        <is>
+          <t>Electric motor ten kilowatt 415V 3 phase flange mount</t>
+        </is>
+      </c>
+      <c r="K9" s="33" t="inlineStr">
+        <is>
+          <t>SITE-MOTOR</t>
+        </is>
+      </c>
+      <c r="L9" s="33" t="inlineStr">
+        <is>
+          <t>PCS</t>
+        </is>
+      </c>
+      <c r="M9" s="33" t="inlineStr"/>
+      <c r="N9" s="33" t="inlineStr"/>
+      <c r="O9" s="33" t="inlineStr"/>
+      <c r="P9" s="33" t="inlineStr"/>
+      <c r="Q9" s="33" t="inlineStr"/>
+      <c r="R9" s="33" t="inlineStr"/>
+      <c r="S9" s="33" t="inlineStr"/>
+      <c r="T9" s="33" t="inlineStr"/>
+      <c r="U9" s="33" t="inlineStr">
+        <is>
+          <t>8501</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="21" t="n"/>
+      <c r="B10" s="21" t="n"/>
+      <c r="C10" s="21" t="n"/>
+      <c r="D10" s="21" t="n"/>
+      <c r="E10" s="21" t="n"/>
+      <c r="F10" s="21" t="n"/>
+      <c r="G10" s="21" t="n"/>
+      <c r="H10" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="I10" s="28" t="inlineStr">
+        <is>
+          <t>MTR-10K-A</t>
+        </is>
+      </c>
+      <c r="J10" s="29" t="inlineStr">
+        <is>
+          <t>Motor 10 kW 415 V three phase flange mounted</t>
+        </is>
+      </c>
+      <c r="K10" s="28" t="inlineStr">
         <is>
           <t>SITE-MOTOR</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>Deterministic review evidence caused the system to suggest this group; human review is required.</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>Confirmed all records as one identity</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>Walkthrough confirmation on synthetic examples; not quality evidence.</t>
+      <c r="L10" s="28" t="inlineStr">
+        <is>
+          <t>PCS</t>
+        </is>
+      </c>
+      <c r="M10" s="28" t="inlineStr"/>
+      <c r="N10" s="28" t="inlineStr"/>
+      <c r="O10" s="28" t="inlineStr"/>
+      <c r="P10" s="28" t="inlineStr"/>
+      <c r="Q10" s="28" t="inlineStr"/>
+      <c r="R10" s="28" t="inlineStr"/>
+      <c r="S10" s="28" t="inlineStr"/>
+      <c r="T10" s="28" t="inlineStr"/>
+      <c r="U10" s="28" t="inlineStr">
+        <is>
+          <t>8501</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I5"/>
+  <mergeCells count="28">
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="G8:G10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="F8:F10"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1011,887 +1773,957 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W10"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="54" customWidth="1" min="7" max="7"/>
-    <col width="38" customWidth="1" min="8" max="8"/>
-    <col width="42" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="48" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Review Status</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Members</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Sites</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Why Suggested</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Human Decision</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Human Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="35" t="inlineStr">
+        <is>
+          <t>CG-000001</t>
+        </is>
+      </c>
+      <c r="B2" s="36" t="inlineStr">
+        <is>
+          <t>Review Deferred</t>
+        </is>
+      </c>
+      <c r="C2" s="35" t="inlineStr">
+        <is>
+          <t>Review Evidence</t>
+        </is>
+      </c>
+      <c r="D2" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="37" t="inlineStr">
+        <is>
+          <t>SITE-TEMP</t>
+        </is>
+      </c>
+      <c r="F2" s="37" t="inlineStr">
+        <is>
+          <t>Some identity signals match; manual assessment is needed.</t>
+        </is>
+      </c>
+      <c r="G2" s="37" t="inlineStr">
+        <is>
+          <t>Deferred for later review</t>
+        </is>
+      </c>
+      <c r="H2" s="37" t="inlineStr">
+        <is>
+          <t>Walkthrough defer on synthetic examples; additional review is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="35" t="inlineStr">
+        <is>
+          <t>CG-000002</t>
+        </is>
+      </c>
+      <c r="B3" s="38" t="inlineStr">
+        <is>
+          <t>Requires Human Review</t>
+        </is>
+      </c>
+      <c r="C3" s="35" t="inlineStr">
+        <is>
+          <t>Stronger Evidence</t>
+        </is>
+      </c>
+      <c r="D3" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="37" t="inlineStr">
+        <is>
+          <t>SITE-SEAL</t>
+        </is>
+      </c>
+      <c r="F3" s="37" t="inlineStr">
+        <is>
+          <t>Multiple deterministic identity signals support review.</t>
+        </is>
+      </c>
+      <c r="G3" s="37" t="inlineStr">
+        <is>
+          <t>Not yet reviewed</t>
+        </is>
+      </c>
+      <c r="H3" s="37" t="inlineStr"/>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="35" t="inlineStr">
+        <is>
+          <t>CG-000003</t>
+        </is>
+      </c>
+      <c r="B4" s="39" t="inlineStr">
+        <is>
+          <t>Human Rejected Candidate</t>
+        </is>
+      </c>
+      <c r="C4" s="35" t="inlineStr">
+        <is>
+          <t>Review Evidence</t>
+        </is>
+      </c>
+      <c r="D4" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="37" t="inlineStr">
+        <is>
+          <t>SITE-GEN-FILTER</t>
+        </is>
+      </c>
+      <c r="F4" s="37" t="inlineStr">
+        <is>
+          <t>Some identity signals match; manual assessment is needed.</t>
+        </is>
+      </c>
+      <c r="G4" s="37" t="inlineStr">
+        <is>
+          <t>Rejected and kept separate</t>
+        </is>
+      </c>
+      <c r="H4" s="37" t="inlineStr">
+        <is>
+          <t>Walkthrough rejection on synthetic examples; records remain separate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="35" t="inlineStr">
+        <is>
+          <t>CG-000004</t>
+        </is>
+      </c>
+      <c r="B5" s="40" t="inlineStr">
+        <is>
+          <t>Human Confirmed Same-Identity Group</t>
+        </is>
+      </c>
+      <c r="C5" s="35" t="inlineStr">
+        <is>
+          <t>Review Evidence</t>
+        </is>
+      </c>
+      <c r="D5" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="37" t="inlineStr">
+        <is>
+          <t>SITE-MOTOR</t>
+        </is>
+      </c>
+      <c r="F5" s="37" t="inlineStr">
+        <is>
+          <t>Some identity signals match; manual assessment is needed.</t>
+        </is>
+      </c>
+      <c r="G5" s="37" t="inlineStr">
+        <is>
+          <t>Confirmed all records as one identity</t>
+        </is>
+      </c>
+      <c r="H5" s="37" t="inlineStr">
+        <is>
+          <t>Walkthrough confirmation on synthetic examples; not quality evidence.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
     <col width="20" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="20" customWidth="1" min="21" max="21"/>
-    <col width="18" customWidth="1" min="22" max="22"/>
-    <col width="48" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="34" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Candidate Group ID</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="B1" s="5" t="inlineStr">
         <is>
-          <t>Canonical Group ID</t>
+          <t>Review Status</t>
         </is>
       </c>
       <c r="C1" s="5" t="inlineStr">
         <is>
-          <t>Review State</t>
+          <t>Evidence</t>
         </is>
       </c>
       <c r="D1" s="5" t="inlineStr">
         <is>
-          <t>System Evidence Tier</t>
+          <t>Members</t>
         </is>
       </c>
       <c r="E1" s="5" t="inlineStr">
         <is>
-          <t>Member Count</t>
+          <t>Group Sites</t>
         </is>
       </c>
       <c r="F1" s="5" t="inlineStr">
         <is>
-          <t>Sites</t>
+          <t>Human Decision</t>
         </is>
       </c>
       <c r="G1" s="5" t="inlineStr">
         <is>
-          <t>Primary Reason</t>
+          <t>Human Comment</t>
         </is>
       </c>
       <c r="H1" s="5" t="inlineStr">
         <is>
-          <t>Human Decision</t>
+          <t>Part Number</t>
         </is>
       </c>
       <c r="I1" s="5" t="inlineStr">
         <is>
-          <t>Human Comment</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="J1" s="5" t="inlineStr">
         <is>
-          <t>Part No</t>
+          <t>Site</t>
         </is>
       </c>
       <c r="K1" s="5" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Inventory UOM</t>
         </is>
       </c>
       <c r="L1" s="5" t="inlineStr">
         <is>
-          <t>Site</t>
+          <t>Part Type</t>
         </is>
       </c>
       <c r="M1" s="5" t="inlineStr">
         <is>
-          <t>Inventory UOM</t>
+          <t>Commodity Group 01</t>
         </is>
       </c>
       <c r="N1" s="5" t="inlineStr">
         <is>
-          <t>Part Type</t>
+          <t>Commodity Group 02</t>
         </is>
       </c>
       <c r="O1" s="5" t="inlineStr">
         <is>
-          <t>Commodity Group 01</t>
+          <t>Safety Code</t>
         </is>
       </c>
       <c r="P1" s="5" t="inlineStr">
         <is>
-          <t>Commodity Group 02</t>
+          <t>Accounting Group</t>
         </is>
       </c>
       <c r="Q1" s="5" t="inlineStr">
         <is>
-          <t>Safety Code</t>
+          <t>Product Code</t>
         </is>
       </c>
       <c r="R1" s="5" t="inlineStr">
         <is>
-          <t>Accounting Group</t>
+          <t>Product Family</t>
         </is>
       </c>
       <c r="S1" s="5" t="inlineStr">
         <is>
-          <t>Product Code</t>
+          <t>Product Category</t>
         </is>
       </c>
       <c r="T1" s="5" t="inlineStr">
         <is>
-          <t>Product Family</t>
-        </is>
-      </c>
-      <c r="U1" s="5" t="inlineStr">
-        <is>
-          <t>Product Category</t>
-        </is>
-      </c>
-      <c r="V1" s="5" t="inlineStr">
-        <is>
           <t>HSN/SAC Code</t>
         </is>
       </c>
-      <c r="W1" s="5" t="inlineStr">
-        <is>
-          <t>Source Row / Stable Record Reference</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="35" t="inlineStr">
         <is>
           <t>CG-000001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>igk1.eyJnIjoiZzJ2Mi1ncm91cC0xMjI1ZGUzNzUzMWNlNTg3ZThiNzBhNjIzNDE0NjYxMzI2OWJmOTM1ZTIyYTQzNTQxMTI3YzE0ZWUzZWEwNGU2IiwicCI6IkcyX1YyIiwicyI6MX0</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" s="36" t="inlineStr">
         <is>
           <t>Review Deferred</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="C2" s="35" t="inlineStr">
         <is>
           <t>Review Evidence</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="D2" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="E2" s="37" t="inlineStr">
         <is>
           <t>SITE-TEMP</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Deterministic review evidence caused the system to suggest this group; human review is required.</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="F2" s="37" t="inlineStr">
         <is>
           <t>Deferred for later review</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="G2" s="37" t="inlineStr">
         <is>
           <t>Walkthrough defer on synthetic examples; additional review is required.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="H2" s="35" t="inlineStr">
         <is>
           <t>TS-PT100-A</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="I2" s="37" t="inlineStr">
         <is>
           <t>Temp sns PT100 0-200 C</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="J2" s="35" t="inlineStr">
         <is>
           <t>SITE-TEMP</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="K2" s="35" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr"/>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="L2" s="35" t="inlineStr"/>
+      <c r="M2" s="35" t="inlineStr"/>
+      <c r="N2" s="35" t="inlineStr"/>
+      <c r="O2" s="35" t="inlineStr"/>
+      <c r="P2" s="35" t="inlineStr"/>
+      <c r="Q2" s="35" t="inlineStr"/>
+      <c r="R2" s="35" t="inlineStr"/>
+      <c r="S2" s="35" t="inlineStr"/>
+      <c r="T2" s="35" t="inlineStr">
         <is>
           <t>9025</t>
         </is>
       </c>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>Row 11 / 349598738fb36d602979c955fea2acbd7c5ae946b6b4218c3f20084b8a40e575</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="35" t="inlineStr">
         <is>
           <t>CG-000001</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>igk1.eyJnIjoiZzJ2Mi1ncm91cC0xMjI1ZGUzNzUzMWNlNTg3ZThiNzBhNjIzNDE0NjYxMzI2OWJmOTM1ZTIyYTQzNTQxMTI3YzE0ZWUzZWEwNGU2IiwicCI6IkcyX1YyIiwicyI6MX0</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B3" s="36" t="inlineStr">
         <is>
           <t>Review Deferred</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="C3" s="35" t="inlineStr">
         <is>
           <t>Review Evidence</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="D3" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="E3" s="37" t="inlineStr">
         <is>
           <t>SITE-TEMP</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Deterministic review evidence caused the system to suggest this group; human review is required.</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="F3" s="37" t="inlineStr">
         <is>
           <t>Deferred for later review</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="G3" s="37" t="inlineStr">
         <is>
           <t>Walkthrough defer on synthetic examples; additional review is required.</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="H3" s="35" t="inlineStr">
         <is>
           <t>SENSOR-PT100-B</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="I3" s="37" t="inlineStr">
         <is>
           <t>Temperature sensor PT100 range 0 to 200 C</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="J3" s="35" t="inlineStr">
         <is>
           <t>SITE-TEMP</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="K3" s="35" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr"/>
-      <c r="T3" s="2" t="inlineStr"/>
-      <c r="U3" s="2" t="inlineStr"/>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="L3" s="35" t="inlineStr"/>
+      <c r="M3" s="35" t="inlineStr"/>
+      <c r="N3" s="35" t="inlineStr"/>
+      <c r="O3" s="35" t="inlineStr"/>
+      <c r="P3" s="35" t="inlineStr"/>
+      <c r="Q3" s="35" t="inlineStr"/>
+      <c r="R3" s="35" t="inlineStr"/>
+      <c r="S3" s="35" t="inlineStr"/>
+      <c r="T3" s="35" t="inlineStr">
         <is>
           <t>9025</t>
         </is>
       </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>Row 12 / 41f70a4b1f7853c0d9d0dac0ea4c4f09d1ccb4fe492057e50453b9488c7929d4</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>CG-000002</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>igk1.eyJnIjoiZzJ2Mi1ncm91cC02NzkzMTdlNTY2MzVmYzRmNGI2NjQ4MGJmMTZjZTY2N2Y4MGJmNWUwOTk2YWJhOTI0YjhhYzBlZTg3NmMzZjExIiwicCI6IkcyX1YyIiwicyI6MX0</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="B4" s="38" t="inlineStr">
         <is>
           <t>Requires Human Review</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
         <is>
           <t>Stronger Evidence</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="D4" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="E4" s="37" t="inlineStr">
         <is>
           <t>SITE-SEAL</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Stronger deterministic evidence caused the system to suggest this group for human review.</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="F4" s="37" t="inlineStr">
         <is>
           <t>Not yet reviewed</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="G4" s="37" t="inlineStr"/>
+      <c r="H4" s="35" t="inlineStr">
         <is>
           <t>SEAL-32-A</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="I4" s="37" t="inlineStr">
         <is>
           <t>Mechanical seal for pump shaft 32 mm</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="J4" s="35" t="inlineStr">
         <is>
           <t>SITE-SEAL</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="K4" s="35" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="2" t="inlineStr"/>
-      <c r="T4" s="2" t="inlineStr"/>
-      <c r="U4" s="2" t="inlineStr"/>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="L4" s="35" t="inlineStr"/>
+      <c r="M4" s="35" t="inlineStr"/>
+      <c r="N4" s="35" t="inlineStr"/>
+      <c r="O4" s="35" t="inlineStr"/>
+      <c r="P4" s="35" t="inlineStr"/>
+      <c r="Q4" s="35" t="inlineStr"/>
+      <c r="R4" s="35" t="inlineStr"/>
+      <c r="S4" s="35" t="inlineStr"/>
+      <c r="T4" s="35" t="inlineStr">
         <is>
           <t>8484</t>
         </is>
       </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>Row 15 / 593e19de9f2f63799fabb9893f622de29fe46861aed914d97a6a4b05d738a4a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>CG-000002</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>igk1.eyJnIjoiZzJ2Mi1ncm91cC02NzkzMTdlNTY2MzVmYzRmNGI2NjQ4MGJmMTZjZTY2N2Y4MGJmNWUwOTk2YWJhOTI0YjhhYzBlZTg3NmMzZjExIiwicCI6IkcyX1YyIiwicyI6MX0</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B5" s="38" t="inlineStr">
         <is>
           <t>Requires Human Review</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="C5" s="35" t="inlineStr">
         <is>
           <t>Stronger Evidence</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="D5" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="E5" s="37" t="inlineStr">
         <is>
           <t>SITE-SEAL</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Stronger deterministic evidence caused the system to suggest this group for human review.</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="F5" s="37" t="inlineStr">
         <is>
           <t>Not yet reviewed</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="G5" s="37" t="inlineStr"/>
+      <c r="H5" s="35" t="inlineStr">
         <is>
           <t>MECH-SEAL-32B</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="I5" s="37" t="inlineStr">
         <is>
           <t>Pump mechanical seal 32mm shaft</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="J5" s="35" t="inlineStr">
         <is>
           <t>SITE-SEAL</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="K5" s="35" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="2" t="inlineStr"/>
-      <c r="T5" s="2" t="inlineStr"/>
-      <c r="U5" s="2" t="inlineStr"/>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="L5" s="35" t="inlineStr"/>
+      <c r="M5" s="35" t="inlineStr"/>
+      <c r="N5" s="35" t="inlineStr"/>
+      <c r="O5" s="35" t="inlineStr"/>
+      <c r="P5" s="35" t="inlineStr"/>
+      <c r="Q5" s="35" t="inlineStr"/>
+      <c r="R5" s="35" t="inlineStr"/>
+      <c r="S5" s="35" t="inlineStr"/>
+      <c r="T5" s="35" t="inlineStr">
         <is>
           <t>8484</t>
         </is>
       </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>Row 16 / 6b9cbff92edea51e7441338ee57a3bbdc3c10e41d5f7cd0bb87eb1d449f0d4e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>CG-000003</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>igk1.eyJnIjoiZzJ2Mi1ncm91cC1iZTJmMTEzZjNmOWUyMjc2YzQxMzQ5MjQyMGU3NWQxYWE2NjUxYTc2NDFhNDNlYTczZjU5OTAxNmEyYWQ5NzU1IiwicCI6IkcyX1YyIiwicyI6MX0</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="B6" s="39" t="inlineStr">
         <is>
           <t>Human Rejected Candidate</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>Review Evidence</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="D6" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="E6" s="37" t="inlineStr">
         <is>
           <t>SITE-GEN-FILTER</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Deterministic review evidence caused the system to suggest this group; human review is required.</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="F6" s="37" t="inlineStr">
         <is>
           <t>Rejected and kept separate</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="G6" s="37" t="inlineStr">
         <is>
           <t>Walkthrough rejection on synthetic examples; records remain separate.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="H6" s="35" t="inlineStr">
         <is>
           <t>FILTER-220-B</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="I6" s="37" t="inlineStr">
         <is>
           <t>Generator oil filter element model 220</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="J6" s="35" t="inlineStr">
         <is>
           <t>SITE-GEN-FILTER</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="K6" s="35" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr"/>
-      <c r="U6" s="2" t="inlineStr"/>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="L6" s="35" t="inlineStr"/>
+      <c r="M6" s="35" t="inlineStr"/>
+      <c r="N6" s="35" t="inlineStr"/>
+      <c r="O6" s="35" t="inlineStr"/>
+      <c r="P6" s="35" t="inlineStr"/>
+      <c r="Q6" s="35" t="inlineStr"/>
+      <c r="R6" s="35" t="inlineStr"/>
+      <c r="S6" s="35" t="inlineStr"/>
+      <c r="T6" s="35" t="inlineStr">
         <is>
           <t>8421</t>
         </is>
       </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>Row 4 / 531002e4594754abc46f59b91764d577a287f2d954695fcaf7d6eeea06d5ac32</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>CG-000003</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>igk1.eyJnIjoiZzJ2Mi1ncm91cC1iZTJmMTEzZjNmOWUyMjc2YzQxMzQ5MjQyMGU3NWQxYWE2NjUxYTc2NDFhNDNlYTczZjU5OTAxNmEyYWQ5NzU1IiwicCI6IkcyX1YyIiwicyI6MX0</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>Human Rejected Candidate</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="C7" s="35" t="inlineStr">
         <is>
           <t>Review Evidence</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="D7" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="E7" s="37" t="inlineStr">
         <is>
           <t>SITE-GEN-FILTER</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Deterministic review evidence caused the system to suggest this group; human review is required.</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="F7" s="37" t="inlineStr">
         <is>
           <t>Rejected and kept separate</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="G7" s="37" t="inlineStr">
         <is>
           <t>Walkthrough rejection on synthetic examples; records remain separate.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="H7" s="35" t="inlineStr">
         <is>
           <t>GOF-220-A</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="I7" s="37" t="inlineStr">
         <is>
           <t>Gen oil fltr element model 220</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="J7" s="35" t="inlineStr">
         <is>
           <t>SITE-GEN-FILTER</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="K7" s="35" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr"/>
-      <c r="S7" s="2" t="inlineStr"/>
-      <c r="T7" s="2" t="inlineStr"/>
-      <c r="U7" s="2" t="inlineStr"/>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="L7" s="35" t="inlineStr"/>
+      <c r="M7" s="35" t="inlineStr"/>
+      <c r="N7" s="35" t="inlineStr"/>
+      <c r="O7" s="35" t="inlineStr"/>
+      <c r="P7" s="35" t="inlineStr"/>
+      <c r="Q7" s="35" t="inlineStr"/>
+      <c r="R7" s="35" t="inlineStr"/>
+      <c r="S7" s="35" t="inlineStr"/>
+      <c r="T7" s="35" t="inlineStr">
         <is>
           <t>8421</t>
         </is>
       </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>Row 3 / 8a0afc4161029767660313523eec583a97d047ccaac3ab259406c3aa9b78e012</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>CG-000004</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>igk1.eyJnIjoiZzJ2Mi1ncm91cC1lNTM4MzJiZjMwMzNmNTVhNzZkMDI2YTFkYjNmODI2ZDI5NzhhNDk4OTU1N2U5Y2Y5OWYzNDE4NmU0Nzc3ZTM3IiwicCI6IkcyX1YyIiwicyI6MX0</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>Human Confirmed Same-Identity Group</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="C8" s="35" t="inlineStr">
         <is>
           <t>Review Evidence</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="D8" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="E8" s="37" t="inlineStr">
         <is>
           <t>SITE-MOTOR</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Deterministic review evidence caused the system to suggest this group; human review is required.</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="F8" s="37" t="inlineStr">
         <is>
           <t>Confirmed all records as one identity</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="G8" s="37" t="inlineStr">
         <is>
           <t>Walkthrough confirmation on synthetic examples; not quality evidence.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="H8" s="35" t="inlineStr">
         <is>
           <t>MTR10K-C</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="I8" s="37" t="inlineStr">
         <is>
           <t>Three phase electric motor 10 kW 415 V flange mounted</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="J8" s="35" t="inlineStr">
         <is>
           <t>SITE-MOTOR</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="K8" s="35" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="2" t="inlineStr"/>
-      <c r="S8" s="2" t="inlineStr"/>
-      <c r="T8" s="2" t="inlineStr"/>
-      <c r="U8" s="2" t="inlineStr"/>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="L8" s="35" t="inlineStr"/>
+      <c r="M8" s="35" t="inlineStr"/>
+      <c r="N8" s="35" t="inlineStr"/>
+      <c r="O8" s="35" t="inlineStr"/>
+      <c r="P8" s="35" t="inlineStr"/>
+      <c r="Q8" s="35" t="inlineStr"/>
+      <c r="R8" s="35" t="inlineStr"/>
+      <c r="S8" s="35" t="inlineStr"/>
+      <c r="T8" s="35" t="inlineStr">
         <is>
           <t>8501</t>
         </is>
       </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>Row 2 / 1facab6e96dcf8b0849828803ad1d3a8754619533426804dfbd2adcd9656addf</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>CG-000004</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>igk1.eyJnIjoiZzJ2Mi1ncm91cC1lNTM4MzJiZjMwMzNmNTVhNzZkMDI2YTFkYjNmODI2ZDI5NzhhNDk4OTU1N2U5Y2Y5OWYzNDE4NmU0Nzc3ZTM3IiwicCI6IkcyX1YyIiwicyI6MX0</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>Human Confirmed Same-Identity Group</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="C9" s="35" t="inlineStr">
         <is>
           <t>Review Evidence</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="D9" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="E9" s="37" t="inlineStr">
         <is>
           <t>SITE-MOTOR</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>Deterministic review evidence caused the system to suggest this group; human review is required.</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="F9" s="37" t="inlineStr">
         <is>
           <t>Confirmed all records as one identity</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="G9" s="37" t="inlineStr">
         <is>
           <t>Walkthrough confirmation on synthetic examples; not quality evidence.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="H9" s="35" t="inlineStr">
         <is>
           <t>MOTOR10K-B</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="I9" s="37" t="inlineStr">
         <is>
           <t>Electric motor ten kilowatt 415V 3 phase flange mount</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="J9" s="35" t="inlineStr">
         <is>
           <t>SITE-MOTOR</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="K9" s="35" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="2" t="inlineStr"/>
-      <c r="S9" s="2" t="inlineStr"/>
-      <c r="T9" s="2" t="inlineStr"/>
-      <c r="U9" s="2" t="inlineStr"/>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="L9" s="35" t="inlineStr"/>
+      <c r="M9" s="35" t="inlineStr"/>
+      <c r="N9" s="35" t="inlineStr"/>
+      <c r="O9" s="35" t="inlineStr"/>
+      <c r="P9" s="35" t="inlineStr"/>
+      <c r="Q9" s="35" t="inlineStr"/>
+      <c r="R9" s="35" t="inlineStr"/>
+      <c r="S9" s="35" t="inlineStr"/>
+      <c r="T9" s="35" t="inlineStr">
         <is>
           <t>8501</t>
         </is>
       </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>Row 1 / 65201026a78c8c51881d7c583d65425d202338772df6a40b910207304650f3db</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>CG-000004</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>igk1.eyJnIjoiZzJ2Mi1ncm91cC1lNTM4MzJiZjMwMzNmNTVhNzZkMDI2YTFkYjNmODI2ZDI5NzhhNDk4OTU1N2U5Y2Y5OWYzNDE4NmU0Nzc3ZTM3IiwicCI6IkcyX1YyIiwicyI6MX0</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="B10" s="40" t="inlineStr">
         <is>
           <t>Human Confirmed Same-Identity Group</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="C10" s="35" t="inlineStr">
         <is>
           <t>Review Evidence</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="D10" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="E10" s="37" t="inlineStr">
         <is>
           <t>SITE-MOTOR</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>Deterministic review evidence caused the system to suggest this group; human review is required.</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="F10" s="37" t="inlineStr">
         <is>
           <t>Confirmed all records as one identity</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="G10" s="37" t="inlineStr">
         <is>
           <t>Walkthrough confirmation on synthetic examples; not quality evidence.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="H10" s="35" t="inlineStr">
         <is>
           <t>MTR-10K-A</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="I10" s="37" t="inlineStr">
         <is>
           <t>Motor 10 kW 415 V three phase flange mounted</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="J10" s="35" t="inlineStr">
         <is>
           <t>SITE-MOTOR</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="K10" s="35" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr"/>
-      <c r="S10" s="2" t="inlineStr"/>
-      <c r="T10" s="2" t="inlineStr"/>
-      <c r="U10" s="2" t="inlineStr"/>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="L10" s="35" t="inlineStr"/>
+      <c r="M10" s="35" t="inlineStr"/>
+      <c r="N10" s="35" t="inlineStr"/>
+      <c r="O10" s="35" t="inlineStr"/>
+      <c r="P10" s="35" t="inlineStr"/>
+      <c r="Q10" s="35" t="inlineStr"/>
+      <c r="R10" s="35" t="inlineStr"/>
+      <c r="S10" s="35" t="inlineStr"/>
+      <c r="T10" s="35" t="inlineStr">
         <is>
           <t>8501</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>Row 0 / d2fb9e94c2aa6508921415ac3418f9ae59fb211cb692122f2dd7627a1eb6b5a2</t>
         </is>
       </c>
     </row>
@@ -1901,4 +2733,446 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="58" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Canonical Group ID</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Member #</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Part Number</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Source Row</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Stable Record Reference</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Projection Contract</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Source Projection Run</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Original System Reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="35" t="inlineStr">
+        <is>
+          <t>CG-000001</t>
+        </is>
+      </c>
+      <c r="B2" s="37" t="inlineStr">
+        <is>
+          <t>igk1.eyJnIjoiZzJ2Mi1ncm91cC0xMjI1ZGUzNzUzMWNlNTg3ZThiNzBhNjIzNDE0NjYxMzI2OWJmOTM1ZTIyYTQzNTQxMTI3YzE0ZWUzZWEwNGU2IiwicCI6IkcyX1YyIiwicyI6MX0</t>
+        </is>
+      </c>
+      <c r="C2" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="35" t="inlineStr">
+        <is>
+          <t>TS-PT100-A</t>
+        </is>
+      </c>
+      <c r="E2" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="F2" s="37" t="inlineStr">
+        <is>
+          <t>349598738fb36d602979c955fea2acbd7c5ae946b6b4218c3f20084b8a40e575</t>
+        </is>
+      </c>
+      <c r="G2" s="35" t="inlineStr">
+        <is>
+          <t>G2_V2</t>
+        </is>
+      </c>
+      <c r="H2" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="37" t="inlineStr">
+        <is>
+          <t>Deterministic review evidence caused the system to suggest this group; human review is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="35" t="inlineStr">
+        <is>
+          <t>CG-000001</t>
+        </is>
+      </c>
+      <c r="B3" s="37" t="inlineStr">
+        <is>
+          <t>igk1.eyJnIjoiZzJ2Mi1ncm91cC0xMjI1ZGUzNzUzMWNlNTg3ZThiNzBhNjIzNDE0NjYxMzI2OWJmOTM1ZTIyYTQzNTQxMTI3YzE0ZWUzZWEwNGU2IiwicCI6IkcyX1YyIiwicyI6MX0</t>
+        </is>
+      </c>
+      <c r="C3" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="35" t="inlineStr">
+        <is>
+          <t>SENSOR-PT100-B</t>
+        </is>
+      </c>
+      <c r="E3" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" s="37" t="inlineStr">
+        <is>
+          <t>41f70a4b1f7853c0d9d0dac0ea4c4f09d1ccb4fe492057e50453b9488c7929d4</t>
+        </is>
+      </c>
+      <c r="G3" s="35" t="inlineStr">
+        <is>
+          <t>G2_V2</t>
+        </is>
+      </c>
+      <c r="H3" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="37" t="inlineStr">
+        <is>
+          <t>Deterministic review evidence caused the system to suggest this group; human review is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="35" t="inlineStr">
+        <is>
+          <t>CG-000002</t>
+        </is>
+      </c>
+      <c r="B4" s="37" t="inlineStr">
+        <is>
+          <t>igk1.eyJnIjoiZzJ2Mi1ncm91cC02NzkzMTdlNTY2MzVmYzRmNGI2NjQ4MGJmMTZjZTY2N2Y4MGJmNWUwOTk2YWJhOTI0YjhhYzBlZTg3NmMzZjExIiwicCI6IkcyX1YyIiwicyI6MX0</t>
+        </is>
+      </c>
+      <c r="C4" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="35" t="inlineStr">
+        <is>
+          <t>SEAL-32-A</t>
+        </is>
+      </c>
+      <c r="E4" s="35" t="n">
+        <v>15</v>
+      </c>
+      <c r="F4" s="37" t="inlineStr">
+        <is>
+          <t>593e19de9f2f63799fabb9893f622de29fe46861aed914d97a6a4b05d738a4a2</t>
+        </is>
+      </c>
+      <c r="G4" s="35" t="inlineStr">
+        <is>
+          <t>G2_V2</t>
+        </is>
+      </c>
+      <c r="H4" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="37" t="inlineStr">
+        <is>
+          <t>Stronger deterministic evidence caused the system to suggest this group for human review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="35" t="inlineStr">
+        <is>
+          <t>CG-000002</t>
+        </is>
+      </c>
+      <c r="B5" s="37" t="inlineStr">
+        <is>
+          <t>igk1.eyJnIjoiZzJ2Mi1ncm91cC02NzkzMTdlNTY2MzVmYzRmNGI2NjQ4MGJmMTZjZTY2N2Y4MGJmNWUwOTk2YWJhOTI0YjhhYzBlZTg3NmMzZjExIiwicCI6IkcyX1YyIiwicyI6MX0</t>
+        </is>
+      </c>
+      <c r="C5" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="35" t="inlineStr">
+        <is>
+          <t>MECH-SEAL-32B</t>
+        </is>
+      </c>
+      <c r="E5" s="35" t="n">
+        <v>16</v>
+      </c>
+      <c r="F5" s="37" t="inlineStr">
+        <is>
+          <t>6b9cbff92edea51e7441338ee57a3bbdc3c10e41d5f7cd0bb87eb1d449f0d4e5</t>
+        </is>
+      </c>
+      <c r="G5" s="35" t="inlineStr">
+        <is>
+          <t>G2_V2</t>
+        </is>
+      </c>
+      <c r="H5" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="37" t="inlineStr">
+        <is>
+          <t>Stronger deterministic evidence caused the system to suggest this group for human review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="35" t="inlineStr">
+        <is>
+          <t>CG-000003</t>
+        </is>
+      </c>
+      <c r="B6" s="37" t="inlineStr">
+        <is>
+          <t>igk1.eyJnIjoiZzJ2Mi1ncm91cC1iZTJmMTEzZjNmOWUyMjc2YzQxMzQ5MjQyMGU3NWQxYWE2NjUxYTc2NDFhNDNlYTczZjU5OTAxNmEyYWQ5NzU1IiwicCI6IkcyX1YyIiwicyI6MX0</t>
+        </is>
+      </c>
+      <c r="C6" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="35" t="inlineStr">
+        <is>
+          <t>FILTER-220-B</t>
+        </is>
+      </c>
+      <c r="E6" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="37" t="inlineStr">
+        <is>
+          <t>531002e4594754abc46f59b91764d577a287f2d954695fcaf7d6eeea06d5ac32</t>
+        </is>
+      </c>
+      <c r="G6" s="35" t="inlineStr">
+        <is>
+          <t>G2_V2</t>
+        </is>
+      </c>
+      <c r="H6" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="37" t="inlineStr">
+        <is>
+          <t>Deterministic review evidence caused the system to suggest this group; human review is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="35" t="inlineStr">
+        <is>
+          <t>CG-000003</t>
+        </is>
+      </c>
+      <c r="B7" s="37" t="inlineStr">
+        <is>
+          <t>igk1.eyJnIjoiZzJ2Mi1ncm91cC1iZTJmMTEzZjNmOWUyMjc2YzQxMzQ5MjQyMGU3NWQxYWE2NjUxYTc2NDFhNDNlYTczZjU5OTAxNmEyYWQ5NzU1IiwicCI6IkcyX1YyIiwicyI6MX0</t>
+        </is>
+      </c>
+      <c r="C7" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="35" t="inlineStr">
+        <is>
+          <t>GOF-220-A</t>
+        </is>
+      </c>
+      <c r="E7" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="37" t="inlineStr">
+        <is>
+          <t>8a0afc4161029767660313523eec583a97d047ccaac3ab259406c3aa9b78e012</t>
+        </is>
+      </c>
+      <c r="G7" s="35" t="inlineStr">
+        <is>
+          <t>G2_V2</t>
+        </is>
+      </c>
+      <c r="H7" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="37" t="inlineStr">
+        <is>
+          <t>Deterministic review evidence caused the system to suggest this group; human review is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="35" t="inlineStr">
+        <is>
+          <t>CG-000004</t>
+        </is>
+      </c>
+      <c r="B8" s="37" t="inlineStr">
+        <is>
+          <t>igk1.eyJnIjoiZzJ2Mi1ncm91cC1lNTM4MzJiZjMwMzNmNTVhNzZkMDI2YTFkYjNmODI2ZDI5NzhhNDk4OTU1N2U5Y2Y5OWYzNDE4NmU0Nzc3ZTM3IiwicCI6IkcyX1YyIiwicyI6MX0</t>
+        </is>
+      </c>
+      <c r="C8" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="35" t="inlineStr">
+        <is>
+          <t>MTR10K-C</t>
+        </is>
+      </c>
+      <c r="E8" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="37" t="inlineStr">
+        <is>
+          <t>1facab6e96dcf8b0849828803ad1d3a8754619533426804dfbd2adcd9656addf</t>
+        </is>
+      </c>
+      <c r="G8" s="35" t="inlineStr">
+        <is>
+          <t>G2_V2</t>
+        </is>
+      </c>
+      <c r="H8" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="37" t="inlineStr">
+        <is>
+          <t>Deterministic review evidence caused the system to suggest this group; human review is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="35" t="inlineStr">
+        <is>
+          <t>CG-000004</t>
+        </is>
+      </c>
+      <c r="B9" s="37" t="inlineStr">
+        <is>
+          <t>igk1.eyJnIjoiZzJ2Mi1ncm91cC1lNTM4MzJiZjMwMzNmNTVhNzZkMDI2YTFkYjNmODI2ZDI5NzhhNDk4OTU1N2U5Y2Y5OWYzNDE4NmU0Nzc3ZTM3IiwicCI6IkcyX1YyIiwicyI6MX0</t>
+        </is>
+      </c>
+      <c r="C9" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="35" t="inlineStr">
+        <is>
+          <t>MOTOR10K-B</t>
+        </is>
+      </c>
+      <c r="E9" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="37" t="inlineStr">
+        <is>
+          <t>65201026a78c8c51881d7c583d65425d202338772df6a40b910207304650f3db</t>
+        </is>
+      </c>
+      <c r="G9" s="35" t="inlineStr">
+        <is>
+          <t>G2_V2</t>
+        </is>
+      </c>
+      <c r="H9" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="37" t="inlineStr">
+        <is>
+          <t>Deterministic review evidence caused the system to suggest this group; human review is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
+          <t>CG-000004</t>
+        </is>
+      </c>
+      <c r="B10" s="37" t="inlineStr">
+        <is>
+          <t>igk1.eyJnIjoiZzJ2Mi1ncm91cC1lNTM4MzJiZjMwMzNmNTVhNzZkMDI2YTFkYjNmODI2ZDI5NzhhNDk4OTU1N2U5Y2Y5OWYzNDE4NmU0Nzc3ZTM3IiwicCI6IkcyX1YyIiwicyI6MX0</t>
+        </is>
+      </c>
+      <c r="C10" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="35" t="inlineStr">
+        <is>
+          <t>MTR-10K-A</t>
+        </is>
+      </c>
+      <c r="E10" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="37" t="inlineStr">
+        <is>
+          <t>d2fb9e94c2aa6508921415ac3418f9ae59fb211cb692122f2dd7627a1eb6b5a2</t>
+        </is>
+      </c>
+      <c r="G10" s="35" t="inlineStr">
+        <is>
+          <t>G2_V2</t>
+        </is>
+      </c>
+      <c r="H10" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="37" t="inlineStr">
+        <is>
+          <t>Deterministic review evidence caused the system to suggest this group; human review is required.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I10"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>